--- a/artfynd/A 32154-2026 artfynd.xlsx
+++ b/artfynd/A 32154-2026 artfynd.xlsx
@@ -1019,7 +1019,7 @@
         <v>136381938</v>
       </c>
       <c r="B5" t="n">
-        <v>92050</v>
+        <v>92051</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>

--- a/artfynd/A 32154-2026 artfynd.xlsx
+++ b/artfynd/A 32154-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>136381932</v>
       </c>
       <c r="B2" t="n">
-        <v>79492</v>
+        <v>79505</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -795,7 +795,7 @@
         <v>136381933</v>
       </c>
       <c r="B3" t="n">
-        <v>79492</v>
+        <v>79505</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -907,7 +907,7 @@
         <v>136381942</v>
       </c>
       <c r="B4" t="n">
-        <v>79492</v>
+        <v>79505</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1019,7 +1019,7 @@
         <v>136381938</v>
       </c>
       <c r="B5" t="n">
-        <v>92051</v>
+        <v>92064</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1131,7 +1131,7 @@
         <v>136381935</v>
       </c>
       <c r="B6" t="n">
-        <v>79460</v>
+        <v>79473</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1243,7 +1243,7 @@
         <v>136381936</v>
       </c>
       <c r="B7" t="n">
-        <v>79460</v>
+        <v>79473</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1355,7 +1355,7 @@
         <v>136381937</v>
       </c>
       <c r="B8" t="n">
-        <v>79460</v>
+        <v>79473</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1467,7 +1467,7 @@
         <v>136381940</v>
       </c>
       <c r="B9" t="n">
-        <v>79460</v>
+        <v>79473</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1579,7 +1579,7 @@
         <v>136381941</v>
       </c>
       <c r="B10" t="n">
-        <v>79460</v>
+        <v>79473</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1691,7 +1691,7 @@
         <v>136381943</v>
       </c>
       <c r="B11" t="n">
-        <v>79460</v>
+        <v>79473</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1803,7 +1803,7 @@
         <v>136381930</v>
       </c>
       <c r="B12" t="n">
-        <v>57993</v>
+        <v>58006</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1925,7 +1925,7 @@
         <v>136381934</v>
       </c>
       <c r="B13" t="n">
-        <v>57993</v>
+        <v>58006</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>

--- a/artfynd/A 32154-2026 artfynd.xlsx
+++ b/artfynd/A 32154-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>136381932</v>
       </c>
       <c r="B2" t="n">
-        <v>79505</v>
+        <v>79506</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -795,7 +795,7 @@
         <v>136381933</v>
       </c>
       <c r="B3" t="n">
-        <v>79505</v>
+        <v>79506</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -907,7 +907,7 @@
         <v>136381942</v>
       </c>
       <c r="B4" t="n">
-        <v>79505</v>
+        <v>79506</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1019,7 +1019,7 @@
         <v>136381938</v>
       </c>
       <c r="B5" t="n">
-        <v>92064</v>
+        <v>92065</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1131,7 +1131,7 @@
         <v>136381935</v>
       </c>
       <c r="B6" t="n">
-        <v>79473</v>
+        <v>79474</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1243,7 +1243,7 @@
         <v>136381936</v>
       </c>
       <c r="B7" t="n">
-        <v>79473</v>
+        <v>79474</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1355,7 +1355,7 @@
         <v>136381937</v>
       </c>
       <c r="B8" t="n">
-        <v>79473</v>
+        <v>79474</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1467,7 +1467,7 @@
         <v>136381940</v>
       </c>
       <c r="B9" t="n">
-        <v>79473</v>
+        <v>79474</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1579,7 +1579,7 @@
         <v>136381941</v>
       </c>
       <c r="B10" t="n">
-        <v>79473</v>
+        <v>79474</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1691,7 +1691,7 @@
         <v>136381943</v>
       </c>
       <c r="B11" t="n">
-        <v>79473</v>
+        <v>79474</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
